--- a/backend/datos-indicadores/2025_SAUCES_UNICA.xlsx
+++ b/backend/datos-indicadores/2025_SAUCES_UNICA.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet name="PRIMERO 6" sheetId="1" r:id="rId4"/>
     <sheet name="SEGUNDO 6" sheetId="2" r:id="rId5"/>
-    <sheet name="TERCERO 6" sheetId="3" r:id="rId6"/>
+    <sheet name="TERCERO 7" sheetId="3" r:id="rId6"/>
     <sheet name="CUARTO 8" sheetId="4" r:id="rId7"/>
-    <sheet name="QUINTO 7" sheetId="5" r:id="rId8"/>
+    <sheet name="QUINTO 8" sheetId="5" r:id="rId8"/>
     <sheet name="Worksheet" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
   <si>
     <t>SEDE SAUCES UNICA GRUPO PRIMERO 6</t>
   </si>
@@ -34,13 +34,13 @@
     <t>CASTELLANO (100 %)</t>
   </si>
   <si>
-    <t>INGLÉS-IDIOMA EXTRANJERO (100 %)</t>
+    <t>INGLES (100 %)</t>
   </si>
   <si>
     <t>MATEMATICAS (100 %)</t>
   </si>
   <si>
-    <t>TECNOLOGIA E INFORMATICA (100 %)</t>
+    <t>INFORMATICA Y TECNOLOGIA (100 %)</t>
   </si>
   <si>
     <t>CONVIVENCIA (100 %)</t>
@@ -79,40 +79,52 @@
     <t>Puesto Final</t>
   </si>
   <si>
-    <t>AROCA FORERO DIEGO ALEJANDRO</t>
+    <t>CUBILLOS MORALES ASHLEY IRIANA</t>
   </si>
   <si>
-    <t>SI</t>
+    <t>GOMEZ FONSECA SAMUEL SANTIAGO</t>
   </si>
   <si>
-    <t>BORDA NIETO DEISSY SALOME</t>
+    <t xml:space="preserve">MONEDERO OSPINA SANTIAGO </t>
   </si>
   <si>
-    <t>CORTES QUITORA LIAM SANTIAGO</t>
+    <t>PACHON ROA MIGUEL STEVEN</t>
   </si>
   <si>
-    <t>HERNANDEZ CORDOBA AMY GABRIELA</t>
+    <t>SOTO RODRIGUEZ ELEANI VIRGINA</t>
+  </si>
+  <si>
+    <t>SUAREZ PINILLA JUAN SEBASTIAN</t>
   </si>
   <si>
     <t>SEDE SAUCES UNICA GRUPO SEGUNDO 6</t>
   </si>
   <si>
-    <t>CRUZ RODRIGUEZ MARIA PAUBLA</t>
+    <t>BANQUET PARDO ANGELIQUE JHULIANA</t>
   </si>
   <si>
-    <t>CUBILLOS MORALES ASHLEY IRIANA</t>
+    <t>CLAVIJO MORALES KAREN DAYANA</t>
   </si>
   <si>
-    <t>MOLINA CUERVO ALLISON SAMARA</t>
+    <t>CUBILLOS MORALES IAN MATIAS</t>
   </si>
   <si>
-    <t xml:space="preserve">QUINTERO TORRES ESTEFANIA </t>
+    <t>HERNANDEZ HERRERA JOHAN ANDRES</t>
   </si>
   <si>
-    <t>RIVERA NARANJO DANNA CAMILA</t>
+    <t xml:space="preserve">LOPEZ CORREA ISABELLA </t>
   </si>
   <si>
-    <t>SEDE SAUCES UNICA GRUPO TERCERO 6</t>
+    <t>SANCHEZ CUBILLOS MARIANA SOFIA</t>
+  </si>
+  <si>
+    <t>TORRES GONZALEZ LIAN JADIEL</t>
+  </si>
+  <si>
+    <t>VASQUEZ VILLARREAL DAVID SANTIAGO</t>
+  </si>
+  <si>
+    <t>SEDE SAUCES UNICA GRUPO TERCERO 7</t>
   </si>
   <si>
     <t>CIENCIAS NATURALES (100 %)</t>
@@ -124,43 +136,55 @@
     <t>RELIGION Y ETICA (100 %)</t>
   </si>
   <si>
-    <t>BOGOTA CASTELLANOS LUIS STIVEN</t>
+    <t>ARDILA VELASQUEZ JHOAN SEBASTIAN</t>
   </si>
   <si>
-    <t>GOMEZ FONSECA SAMUEL SANTIAGO</t>
+    <t>HERNANDEZ MENDOZA DEIVI SANTIAGO</t>
   </si>
   <si>
-    <t>PACHON ROA MIGUEL STEVEN</t>
+    <t>LOPEZ VELASQUEZ YILBER JOSE</t>
   </si>
   <si>
-    <t>SOTO RODRIGUEZ ELEANI VIRGINA</t>
-  </si>
-  <si>
-    <t>SUAREZ PINILLA JUAN SEBASTIAN</t>
+    <t>VASQUEZ VILLARREAL YONATAN ALFREDO</t>
   </si>
   <si>
     <t>SEDE SAUCES UNICA GRUPO CUARTO 8</t>
   </si>
   <si>
-    <t>BANQUET PARDO ANGELIQUE JHULIANA</t>
+    <t>AGUDELO GOMEZ EDHY SANTIAGO</t>
   </si>
   <si>
-    <t>CLAVIJO MORALES KAREN DAYANA</t>
+    <t>ALVAREZ CORDOBA HADER LEANDRO</t>
   </si>
   <si>
-    <t>CUBILLOS MORALES IAN MATIAS</t>
+    <t>BELTRAN URREGO REYMAN JEAN PAUL</t>
   </si>
   <si>
-    <t>TORRES GONZALEZ LIAN JADIEL</t>
+    <t>PERALTA CABRERA ALBERT ANTHONY</t>
   </si>
   <si>
-    <t>SEDE SAUCES UNICA GRUPO QUINTO 7</t>
+    <t>REINA SOSA EILIN VIVIANA</t>
   </si>
   <si>
-    <t>ARDILA VELASQUEZ JHOAN SEBASTIAN</t>
+    <t>SANCHEZ HERRERA EVELIN SOFIA</t>
   </si>
   <si>
-    <t>HERNANDEZ MENDOZA DEIVI SANTIAGO</t>
+    <t xml:space="preserve">SUAREZ RAMIREZ NICOL </t>
+  </si>
+  <si>
+    <t>SEDE SAUCES UNICA GRUPO QUINTO 8</t>
+  </si>
+  <si>
+    <t>CHINGATE  VALERY SOFIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ TELLEZ KAREN SOFIA</t>
+  </si>
+  <si>
+    <t>RUIZ BARACALDO MICHELLE VALERIA</t>
+  </si>
+  <si>
+    <t>VILLALOBOS CHINGATE ZAIRA VALENTINA</t>
   </si>
 </sst>
 </file>
@@ -200,7 +224,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,19 +252,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor rgb="FFffff99"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF88C4FF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFAD82"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -265,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -284,6 +302,9 @@
     <xf xfId="0" fontId="0" numFmtId="164" fillId="4" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="5" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -298,12 +319,6 @@
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" textRotation="90" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="5" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="6" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -604,7 +619,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AP12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="2.285156" bestFit="true" customWidth="true" style="0"/>
@@ -655,11 +670,11 @@
     <row r="3" spans="1:42" hidden="true"/>
     <row r="4" spans="1:42" hidden="true"/>
     <row r="5" spans="1:42" customHeight="1" ht="100">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="8"/>
       <c r="D5" s="2" t="s">
         <v>1</v>
       </c>
@@ -709,136 +724,136 @@
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
-      <c r="AM5" s="7"/>
-      <c r="AN5" s="7"/>
-      <c r="AO5" s="7"/>
-      <c r="AP5" s="7"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="10" t="s">
+      <c r="V6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="W6" s="10" t="s">
+      <c r="W6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="X6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Y6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Z6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AA6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="9" t="s">
+      <c r="AC6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="10" t="s">
+      <c r="AD6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AE6" s="10" t="s">
+      <c r="AE6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AF6" s="10" t="s">
+      <c r="AF6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AG6" s="10" t="s">
+      <c r="AG6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AH6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AI6" s="10" t="s">
+      <c r="AI6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AJ6" s="10" t="s">
+      <c r="AJ6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AK6" s="10" t="s">
+      <c r="AK6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AL6" s="10" t="s">
+      <c r="AL6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="10" t="s">
+      <c r="AM6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AN6" s="10" t="s">
+      <c r="AN6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="AO6" s="10" t="s">
+      <c r="AO6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AP6" s="7"/>
+      <c r="AP6" s="8"/>
     </row>
     <row r="7" spans="1:42">
       <c r="A7" s="1">
@@ -847,95 +862,93 @@
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="4">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="E7" s="4">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="F7" s="4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="5">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="4">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J7" s="4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K7" s="4">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="L7" s="5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M7" s="1"/>
-      <c r="N7" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="O7" s="4">
-        <v>3.7</v>
+      <c r="N7" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="O7" s="6">
+        <v>2.1</v>
       </c>
       <c r="P7" s="4">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" s="5">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="4">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T7" s="4">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U7" s="4">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V7" s="5">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="W7" s="1"/>
-      <c r="X7" s="4">
-        <v>4</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>4</v>
+      <c r="X7" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>2.6</v>
       </c>
       <c r="Z7" s="4">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="4">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" s="4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AE7" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AF7" s="5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="4">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AI7" s="4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AJ7" s="4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AK7" s="5">
         <v>3.6</v>
@@ -944,8 +957,8 @@
       <c r="AM7" s="1">
         <v>0</v>
       </c>
-      <c r="AN7" s="6">
-        <v>3.767</v>
+      <c r="AN7" s="7">
+        <v>3.567</v>
       </c>
       <c r="AO7" s="1">
         <v>4</v>
@@ -956,108 +969,108 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="4">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="E8" s="4">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="F8" s="4">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="G8" s="5">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J8" s="4">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="K8" s="4">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L8" s="5">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="M8" s="1"/>
-      <c r="N8" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="O8" s="4">
-        <v>4.7</v>
+      <c r="N8" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="O8" s="6">
+        <v>2.5</v>
       </c>
       <c r="P8" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" s="5">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="4">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="T8" s="4">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="U8" s="4">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="V8" s="5">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="4">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="Y8" s="4">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Z8" s="4">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" s="5">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="4">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" s="4">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AE8" s="4">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AF8" s="5">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="4">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AI8" s="4">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AJ8" s="4">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AK8" s="5">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1">
         <v>0</v>
       </c>
-      <c r="AN8" s="6">
-        <v>4.683</v>
+      <c r="AN8" s="7">
+        <v>3.417</v>
       </c>
       <c r="AO8" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:42">
@@ -1065,108 +1078,108 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="4">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="E9" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G9" s="5">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="4">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J9" s="4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K9" s="4">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="L9" s="5">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="4">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O9" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P9" s="4">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="5">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="4">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T9" s="4">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="U9" s="4">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="V9" s="5">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="W9" s="1"/>
       <c r="X9" s="4">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Y9" s="4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="Z9" s="4">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" s="5">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AB9" s="1"/>
       <c r="AC9" s="4">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" s="4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AE9" s="4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AF9" s="5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AI9" s="4">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AJ9" s="4">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AK9" s="5">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1">
         <v>0</v>
       </c>
-      <c r="AN9" s="6">
-        <v>3.983</v>
+      <c r="AN9" s="7">
+        <v>4.483</v>
       </c>
       <c r="AO9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:42">
@@ -1174,108 +1187,326 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="4">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="G10" s="5">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="4">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J10" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="4">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L10" s="5">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="M10" s="1"/>
-      <c r="N10" s="4">
-        <v>4.1</v>
+      <c r="N10" s="6">
+        <v>2.1</v>
       </c>
       <c r="O10" s="4">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P10" s="4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" s="5">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="R10" s="1"/>
-      <c r="S10" s="4">
-        <v>4.1</v>
+      <c r="S10" s="6">
+        <v>2.8</v>
       </c>
       <c r="T10" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="U10" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="V10" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="W10" s="1"/>
+      <c r="X10" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AD10" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="4">
         <v>4.4</v>
       </c>
-      <c r="U10" s="4">
-        <v>4</v>
-      </c>
-      <c r="V10" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="W10" s="1"/>
-      <c r="X10" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>4.4</v>
-      </c>
-      <c r="Z10" s="4">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="AD10" s="4">
-        <v>4</v>
-      </c>
-      <c r="AE10" s="4">
-        <v>4.3</v>
-      </c>
       <c r="AF10" s="5">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AG10" s="1"/>
       <c r="AH10" s="4">
         <v>3</v>
       </c>
       <c r="AI10" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AJ10" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK10" s="5">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1">
         <v>0</v>
       </c>
-      <c r="AN10" s="6">
-        <v>4.183</v>
+      <c r="AN10" s="7">
+        <v>3.217</v>
       </c>
       <c r="AO10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="F11" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="J11" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="K11" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="4">
+        <v>3</v>
+      </c>
+      <c r="O11" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="P11" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="T11" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="U11" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="V11" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="W11" s="1"/>
+      <c r="X11" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AD11" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="4">
+        <v>4</v>
+      </c>
+      <c r="AI11" s="4">
+        <v>4</v>
+      </c>
+      <c r="AJ11" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK11" s="5">
+        <v>4</v>
+      </c>
+      <c r="AL11" s="1"/>
+      <c r="AM11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="7">
+        <v>3.85</v>
+      </c>
+      <c r="AO11" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:42">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="F12" s="4">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="J12" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K12" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="O12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="P12" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="T12" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="U12" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="V12" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="W12" s="1"/>
+      <c r="X12" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AE12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AI12" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AJ12" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="AK12" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="7">
+        <v>3.833</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1308,7 +1539,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AP11"/>
+  <dimension ref="A1:AP14"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="2.285156" bestFit="true" customWidth="true" style="0"/>
@@ -1359,11 +1590,11 @@
     <row r="3" spans="1:42" hidden="true"/>
     <row r="4" spans="1:42" hidden="true"/>
     <row r="5" spans="1:42" customHeight="1" ht="100">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1413,163 +1644,163 @@
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
-      <c r="AM5" s="7"/>
-      <c r="AN5" s="7"/>
-      <c r="AO5" s="7"/>
-      <c r="AP5" s="7"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="10" t="s">
+      <c r="V6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="W6" s="10" t="s">
+      <c r="W6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="X6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Y6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Z6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AA6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="9" t="s">
+      <c r="AC6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="10" t="s">
+      <c r="AD6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AE6" s="10" t="s">
+      <c r="AE6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AF6" s="10" t="s">
+      <c r="AF6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AG6" s="10" t="s">
+      <c r="AG6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AH6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AI6" s="10" t="s">
+      <c r="AI6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AJ6" s="10" t="s">
+      <c r="AJ6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AK6" s="10" t="s">
+      <c r="AK6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AL6" s="10" t="s">
+      <c r="AL6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="10" t="s">
+      <c r="AM6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AN6" s="10" t="s">
+      <c r="AN6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="AO6" s="10" t="s">
+      <c r="AO6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AP6" s="7"/>
+      <c r="AP6" s="8"/>
     </row>
     <row r="7" spans="1:42">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="E7" s="4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="F7" s="4">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="G7" s="5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J7" s="4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K7" s="4">
         <v>4</v>
@@ -1579,78 +1810,78 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="4">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O7" s="4">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7" s="4">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" s="5">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="4">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="4">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U7" s="4">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="V7" s="5">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="W7" s="1"/>
       <c r="X7" s="4">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y7" s="4">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="Z7" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="5">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD7" s="4">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AE7" s="4">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AF7" s="5">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AI7" s="4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AJ7" s="4">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AK7" s="5">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1">
         <v>0</v>
       </c>
-      <c r="AN7" s="6">
-        <v>4.217</v>
+      <c r="AN7" s="7">
+        <v>3.733</v>
       </c>
       <c r="AO7" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:42">
@@ -1658,108 +1889,108 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="E8" s="4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F8" s="4">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G8" s="5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J8" s="4">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="4">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L8" s="5">
         <v>4.2</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O8" s="4">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P8" s="4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" s="5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T8" s="4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="U8" s="4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="V8" s="5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="4">
         <v>4.2</v>
       </c>
       <c r="Y8" s="4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="Z8" s="4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" s="5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="5">
         <v>4.4</v>
-      </c>
-      <c r="AD8" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="AE8" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="AF8" s="5">
-        <v>4.3</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AI8" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AJ8" s="4">
         <v>4</v>
       </c>
       <c r="AK8" s="5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1">
         <v>0</v>
       </c>
-      <c r="AN8" s="6">
-        <v>4.3</v>
+      <c r="AN8" s="7">
+        <v>4.167</v>
       </c>
       <c r="AO8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:42">
@@ -1767,110 +1998,108 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="4">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="E9" s="4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F9" s="4">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="G9" s="5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="4">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J9" s="4">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K9" s="4">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L9" s="5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M9" s="1"/>
-      <c r="N9" s="11">
-        <v>2.5</v>
+      <c r="N9" s="4">
+        <v>4.8</v>
       </c>
       <c r="O9" s="4">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P9" s="4">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="5">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R9" s="1"/>
-      <c r="S9" s="11">
-        <v>2.8</v>
+      <c r="S9" s="4">
+        <v>4.2</v>
       </c>
       <c r="T9" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="U9" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="V9" s="12">
-        <v>2.9</v>
-      </c>
-      <c r="W9" s="5">
-        <v>3</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="U9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="V9" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="W9" s="1"/>
       <c r="X9" s="4">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="Z9" s="11">
-        <v>2.8</v>
+        <v>4.5</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>4</v>
       </c>
       <c r="AA9" s="5">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AB9" s="1"/>
       <c r="AC9" s="4">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" s="4">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AE9" s="4">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AF9" s="5">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="4">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AI9" s="4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AJ9" s="4">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AK9" s="5">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="7">
+        <v>4.317</v>
+      </c>
+      <c r="AO9" s="1">
         <v>2</v>
-      </c>
-      <c r="AN9" s="6">
-        <v>3.383</v>
-      </c>
-      <c r="AO9" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:42">
@@ -1878,108 +2107,108 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="4">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="E10" s="4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="G10" s="5">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="4">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J10" s="4">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" s="5">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="4">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="O10" s="4">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="P10" s="4">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" s="5">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="4">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T10" s="4">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="U10" s="4">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="V10" s="5">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="W10" s="1"/>
       <c r="X10" s="4">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y10" s="4">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="Z10" s="4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="5">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="4">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD10" s="4">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AE10" s="4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AF10" s="5">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG10" s="1"/>
       <c r="AH10" s="4">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AI10" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AJ10" s="4">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AK10" s="5">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1">
         <v>0</v>
       </c>
-      <c r="AN10" s="6">
-        <v>4.467</v>
+      <c r="AN10" s="7">
+        <v>3.583</v>
       </c>
       <c r="AO10" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:42">
@@ -1987,110 +2216,435 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="4">
         <v>4</v>
       </c>
       <c r="E11" s="4">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="F11" s="4">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G11" s="5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="4">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J11" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K11" s="4">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="O11" s="11">
-        <v>2.8</v>
+        <v>4.2</v>
+      </c>
+      <c r="O11" s="4">
+        <v>4</v>
       </c>
       <c r="P11" s="4">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q11" s="5">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="4">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T11" s="4">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U11" s="4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V11" s="5">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="W11" s="1"/>
       <c r="X11" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="Y11" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="Z11" s="11">
-        <v>2.9</v>
-      </c>
-      <c r="AA11" s="12">
-        <v>2.9</v>
-      </c>
-      <c r="AB11" s="5">
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>4</v>
+      </c>
+      <c r="AB11" s="1"/>
       <c r="AC11" s="4">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AD11" s="4">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AE11" s="4">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AF11" s="5">
         <v>4.1</v>
       </c>
       <c r="AG11" s="1"/>
       <c r="AH11" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI11" s="4">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AJ11" s="4">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AK11" s="5">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="7">
+        <v>4.067</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:42">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="E12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="F12" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4.6</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="J12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="K12" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="O12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="P12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="T12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="U12" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="V12" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="W12" s="1"/>
+      <c r="X12" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="AE12" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="4">
+        <v>5</v>
+      </c>
+      <c r="AI12" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="AJ12" s="4">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="5">
+        <v>4.9</v>
+      </c>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="7">
+        <v>4.417</v>
+      </c>
+      <c r="AO12" s="1">
         <v>1</v>
       </c>
-      <c r="AN11" s="6">
+    </row>
+    <row r="13" spans="1:42">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="J13" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K13" s="4">
+        <v>4</v>
+      </c>
+      <c r="L13" s="5">
+        <v>4</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="O13" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="P13" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="T13" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="U13" s="4">
+        <v>4</v>
+      </c>
+      <c r="V13" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="W13" s="1"/>
+      <c r="X13" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AD13" s="4">
         <v>3.6</v>
       </c>
-      <c r="AO11" s="1">
-        <v>4</v>
+      <c r="AE13" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="4">
+        <v>4</v>
+      </c>
+      <c r="AI13" s="4">
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AK13" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="7">
+        <v>4.15</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="G14" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="K14" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="L14" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="O14" s="6">
+        <v>2</v>
+      </c>
+      <c r="P14" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>2.3</v>
+      </c>
+      <c r="R14" s="1"/>
+      <c r="S14" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="T14" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="U14" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="V14" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="W14" s="1"/>
+      <c r="X14" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="AA14" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="AD14" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AE14" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="AF14" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="4">
+        <v>4</v>
+      </c>
+      <c r="AI14" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AJ14" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK14" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1">
+        <v>4</v>
+      </c>
+      <c r="AN14" s="7">
+        <v>3.067</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2123,7 +2677,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BE11"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="2.285156" bestFit="true" customWidth="true" style="0"/>
@@ -2181,7 +2735,7 @@
     <col min="54" max="54" width="3" customWidth="true" style="0"/>
     <col min="55" max="55" width="7" customWidth="true" style="0"/>
     <col min="56" max="56" width="3" customWidth="true" style="0"/>
-    <col min="2" max="2" width="39.990234" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="41.132813" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:57" hidden="true"/>
@@ -2189,20 +2743,20 @@
     <row r="3" spans="1:57" hidden="true"/>
     <row r="4" spans="1:57" hidden="true"/>
     <row r="5" spans="1:57" customHeight="1" ht="100">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2216,7 +2770,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2264,328 +2818,328 @@
       <c r="AY5" s="3"/>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="3"/>
-      <c r="BB5" s="7"/>
-      <c r="BC5" s="7"/>
-      <c r="BD5" s="7"/>
-      <c r="BE5" s="7"/>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
+      <c r="BD5" s="8"/>
+      <c r="BE5" s="8"/>
     </row>
     <row r="6" spans="1:57">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="10" t="s">
+      <c r="V6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="W6" s="10" t="s">
+      <c r="W6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="X6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Y6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Z6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AA6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="9" t="s">
+      <c r="AC6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="10" t="s">
+      <c r="AD6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AE6" s="10" t="s">
+      <c r="AE6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AF6" s="10" t="s">
+      <c r="AF6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AG6" s="10" t="s">
+      <c r="AG6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AH6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AI6" s="10" t="s">
+      <c r="AI6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AJ6" s="10" t="s">
+      <c r="AJ6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AK6" s="10" t="s">
+      <c r="AK6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AL6" s="10" t="s">
+      <c r="AL6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="9" t="s">
+      <c r="AM6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AN6" s="10" t="s">
+      <c r="AN6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AO6" s="10" t="s">
+      <c r="AO6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AP6" s="10" t="s">
+      <c r="AP6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AQ6" s="10" t="s">
+      <c r="AQ6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AR6" s="9" t="s">
+      <c r="AR6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AS6" s="10" t="s">
+      <c r="AS6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AT6" s="10" t="s">
+      <c r="AT6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AU6" s="10" t="s">
+      <c r="AU6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AV6" s="10" t="s">
+      <c r="AV6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AW6" s="9" t="s">
+      <c r="AW6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AX6" s="10" t="s">
+      <c r="AX6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AY6" s="10" t="s">
+      <c r="AY6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AZ6" s="10" t="s">
+      <c r="AZ6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="BA6" s="10" t="s">
+      <c r="BA6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="BB6" s="10" t="s">
+      <c r="BB6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="BC6" s="10" t="s">
+      <c r="BC6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="BD6" s="10" t="s">
+      <c r="BD6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="BE6" s="7"/>
+      <c r="BE6" s="8"/>
     </row>
     <row r="7" spans="1:57">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="4">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="E7" s="4">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="F7" s="4">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="G7" s="5">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="4">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J7" s="4">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="K7" s="4">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="L7" s="5">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="4">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O7" s="4">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P7" s="4">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" s="5">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="4">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T7" s="4">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U7" s="4">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="V7" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W7" s="1"/>
       <c r="X7" s="4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y7" s="4">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="4">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" s="5">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="4">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE7" s="4">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AF7" s="5">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="4">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AI7" s="4">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="AJ7" s="4">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AK7" s="5">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AL7" s="1"/>
       <c r="AM7" s="4">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AN7" s="4">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AO7" s="4">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AP7" s="5">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="4">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" s="4">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" s="4">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" s="5">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AV7" s="1"/>
       <c r="AW7" s="4">
         <v>3</v>
       </c>
       <c r="AX7" s="4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AY7" s="4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AZ7" s="5">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BA7" s="1"/>
       <c r="BB7" s="1">
         <v>0</v>
       </c>
-      <c r="BC7" s="6">
-        <v>3.156</v>
+      <c r="BC7" s="7">
+        <v>4.289</v>
       </c>
       <c r="BD7" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:57">
@@ -2593,107 +3147,107 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="4">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E8" s="4">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="F8" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="5">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="4">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J8" s="4">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K8" s="4">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L8" s="5">
         <v>3.5</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="4">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O8" s="4">
         <v>3.8</v>
       </c>
       <c r="P8" s="4">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" s="5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T8" s="4">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="U8" s="4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V8" s="5">
         <v>3.3</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="4">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" s="4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z8" s="4">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="5">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB8" s="1"/>
-      <c r="AC8" s="4">
-        <v>3</v>
-      </c>
-      <c r="AD8" s="4">
-        <v>3.3</v>
+      <c r="AC8" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>2.8</v>
       </c>
       <c r="AE8" s="4">
         <v>3</v>
       </c>
       <c r="AF8" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="AG8" s="1"/>
+        <v>2.8</v>
+      </c>
+      <c r="AG8" s="5">
+        <v>32</v>
+      </c>
       <c r="AH8" s="4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AI8" s="4">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AJ8" s="4">
         <v>3</v>
       </c>
       <c r="AK8" s="5">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AL8" s="1"/>
       <c r="AM8" s="4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AN8" s="4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AO8" s="4">
         <v>3</v>
@@ -2703,20 +3257,20 @@
       </c>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="4">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AS8" s="4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AT8" s="4">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AU8" s="5">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AV8" s="1"/>
       <c r="AW8" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AX8" s="4">
         <v>3</v>
@@ -2725,17 +3279,17 @@
         <v>3</v>
       </c>
       <c r="AZ8" s="5">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BA8" s="1"/>
       <c r="BB8" s="1">
         <v>0</v>
       </c>
-      <c r="BC8" s="6">
-        <v>3.5</v>
+      <c r="BC8" s="7">
+        <v>3.367</v>
       </c>
       <c r="BD8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:57">
@@ -2743,147 +3297,147 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="4">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="F9" s="4">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="G9" s="5">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="4">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J9" s="4">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="4">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L9" s="5">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="4">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O9" s="4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P9" s="4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" s="5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="4">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T9" s="4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U9" s="4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V9" s="5">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="W9" s="1"/>
       <c r="X9" s="4">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="Y9" s="4">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Z9" s="4">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" s="5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" s="1"/>
       <c r="AC9" s="4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD9" s="4">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE9" s="4">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AF9" s="5">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AI9" s="4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AJ9" s="4">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AK9" s="5">
         <v>3.9</v>
       </c>
       <c r="AL9" s="1"/>
       <c r="AM9" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AN9" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AO9" s="4">
         <v>3.6</v>
       </c>
-      <c r="AN9" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="AO9" s="11">
-        <v>2.7</v>
-      </c>
       <c r="AP9" s="5">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AQ9" s="1"/>
       <c r="AR9" s="4">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AS9" s="4">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AT9" s="4">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU9" s="5">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AV9" s="1"/>
       <c r="AW9" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AX9" s="4">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AY9" s="4">
         <v>3.5</v>
       </c>
       <c r="AZ9" s="5">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BA9" s="1"/>
       <c r="BB9" s="1">
-        <v>1</v>
-      </c>
-      <c r="BC9" s="6">
-        <v>3.856</v>
+        <v>0</v>
+      </c>
+      <c r="BC9" s="7">
+        <v>3.911</v>
       </c>
       <c r="BD9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:57">
@@ -2891,295 +3445,147 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="4">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4">
-        <v>4.6</v>
-      </c>
-      <c r="F10" s="4">
-        <v>4.1</v>
+      <c r="D10" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2</v>
       </c>
       <c r="G10" s="5">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="J10" s="4">
-        <v>4</v>
-      </c>
-      <c r="K10" s="4">
-        <v>4.5</v>
+      <c r="I10" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="J10" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="K10" s="6">
+        <v>2.5</v>
       </c>
       <c r="L10" s="5">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="4">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O10" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P10" s="4">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" s="5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="4">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="T10" s="4">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="U10" s="4">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="V10" s="5">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="W10" s="1"/>
       <c r="X10" s="4">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Y10" s="4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Z10" s="4">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" s="5">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB10" s="1"/>
-      <c r="AC10" s="4">
-        <v>4.4</v>
-      </c>
-      <c r="AD10" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="AE10" s="4">
-        <v>3.9</v>
+      <c r="AC10" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AE10" s="6">
+        <v>2</v>
       </c>
       <c r="AF10" s="5">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AG10" s="1"/>
-      <c r="AH10" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="AI10" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="AJ10" s="4">
-        <v>4.3</v>
+      <c r="AH10" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="AI10" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="AJ10" s="6">
+        <v>2</v>
       </c>
       <c r="AK10" s="5">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" s="1"/>
-      <c r="AM10" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="AN10" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="AO10" s="4">
-        <v>3.9</v>
+      <c r="AM10" s="6">
+        <v>2.2</v>
+      </c>
+      <c r="AN10" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="AO10" s="6">
+        <v>2.5</v>
       </c>
       <c r="AP10" s="5">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10" s="1"/>
       <c r="AR10" s="4">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AS10" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="AT10" s="4">
-        <v>4.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="AT10" s="6">
+        <v>2.8</v>
       </c>
       <c r="AU10" s="5">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AV10" s="1"/>
       <c r="AW10" s="4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX10" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AY10" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AZ10" s="5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BA10" s="1"/>
       <c r="BB10" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC10" s="6">
-        <v>4.233</v>
+        <v>6</v>
+      </c>
+      <c r="BC10" s="7">
+        <v>3</v>
       </c>
       <c r="BD10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:57">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="E11" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="F11" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="G11" s="5">
-        <v>4.1</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="J11" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="K11" s="4">
-        <v>4.6</v>
-      </c>
-      <c r="L11" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="O11" s="4">
-        <v>4</v>
-      </c>
-      <c r="P11" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q11" s="5">
-        <v>4.1</v>
-      </c>
-      <c r="R11" s="1"/>
-      <c r="S11" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="T11" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="U11" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="V11" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="W11" s="1"/>
-      <c r="X11" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="Y11" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="Z11" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="AA11" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="4">
-        <v>4.4</v>
-      </c>
-      <c r="AD11" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="AE11" s="4">
-        <v>4</v>
-      </c>
-      <c r="AF11" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="AI11" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="AJ11" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="AK11" s="5">
-        <v>4.1</v>
-      </c>
-      <c r="AL11" s="1"/>
-      <c r="AM11" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="AN11" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="AO11" s="4">
-        <v>4.4</v>
-      </c>
-      <c r="AP11" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="AQ11" s="1"/>
-      <c r="AR11" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="AS11" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="AT11" s="4">
-        <v>4.6</v>
-      </c>
-      <c r="AU11" s="5">
-        <v>4.4</v>
-      </c>
-      <c r="AV11" s="1"/>
-      <c r="AW11" s="4">
-        <v>4</v>
-      </c>
-      <c r="AX11" s="4">
-        <v>4</v>
-      </c>
-      <c r="AY11" s="4">
-        <v>4</v>
-      </c>
-      <c r="AZ11" s="5">
-        <v>4</v>
-      </c>
-      <c r="BA11" s="1"/>
-      <c r="BB11" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC11" s="6">
-        <v>4.222</v>
-      </c>
-      <c r="BD11" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3621,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BE13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="2.285156" bestFit="true" customWidth="true" style="0"/>
@@ -3281,20 +3687,20 @@
     <row r="3" spans="1:57" hidden="true"/>
     <row r="4" spans="1:57" hidden="true"/>
     <row r="5" spans="1:57" customHeight="1" ht="100">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -3308,7 +3714,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -3356,328 +3762,328 @@
       <c r="AY5" s="3"/>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="3"/>
-      <c r="BB5" s="7"/>
-      <c r="BC5" s="7"/>
-      <c r="BD5" s="7"/>
-      <c r="BE5" s="7"/>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
+      <c r="BD5" s="8"/>
+      <c r="BE5" s="8"/>
     </row>
     <row r="6" spans="1:57">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="10" t="s">
+      <c r="V6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="W6" s="10" t="s">
+      <c r="W6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="X6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Y6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Z6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AA6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="9" t="s">
+      <c r="AC6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="10" t="s">
+      <c r="AD6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AE6" s="10" t="s">
+      <c r="AE6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AF6" s="10" t="s">
+      <c r="AF6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AG6" s="10" t="s">
+      <c r="AG6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AH6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AI6" s="10" t="s">
+      <c r="AI6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AJ6" s="10" t="s">
+      <c r="AJ6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AK6" s="10" t="s">
+      <c r="AK6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AL6" s="10" t="s">
+      <c r="AL6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="9" t="s">
+      <c r="AM6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AN6" s="10" t="s">
+      <c r="AN6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AO6" s="10" t="s">
+      <c r="AO6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AP6" s="10" t="s">
+      <c r="AP6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AQ6" s="10" t="s">
+      <c r="AQ6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AR6" s="9" t="s">
+      <c r="AR6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AS6" s="10" t="s">
+      <c r="AS6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AT6" s="10" t="s">
+      <c r="AT6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AU6" s="10" t="s">
+      <c r="AU6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AV6" s="10" t="s">
+      <c r="AV6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AW6" s="9" t="s">
+      <c r="AW6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AX6" s="10" t="s">
+      <c r="AX6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AY6" s="10" t="s">
+      <c r="AY6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AZ6" s="10" t="s">
+      <c r="AZ6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="BA6" s="10" t="s">
+      <c r="BA6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="BB6" s="10" t="s">
+      <c r="BB6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="BC6" s="10" t="s">
+      <c r="BC6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="BD6" s="10" t="s">
+      <c r="BD6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="BE6" s="7"/>
+      <c r="BE6" s="8"/>
     </row>
     <row r="7" spans="1:57">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="4">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E7" s="4">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="F7" s="4">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="G7" s="5">
         <v>3.7</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="4">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J7" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="K7" s="11">
-        <v>2.6</v>
+        <v>3.5</v>
+      </c>
+      <c r="K7" s="4">
+        <v>4.2</v>
       </c>
       <c r="L7" s="5">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O7" s="4">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P7" s="4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" s="5">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="4">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T7" s="4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U7" s="4">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="V7" s="5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W7" s="1"/>
       <c r="X7" s="4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y7" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Z7" s="4">
         <v>4.6</v>
       </c>
-      <c r="Z7" s="4">
-        <v>4</v>
-      </c>
       <c r="AA7" s="5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="4">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" s="4">
         <v>3.6</v>
       </c>
       <c r="AE7" s="4">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AF7" s="5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AI7" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AJ7" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="AK7" s="5">
         <v>4.3</v>
-      </c>
-      <c r="AJ7" s="11">
-        <v>2.6</v>
-      </c>
-      <c r="AK7" s="5">
-        <v>3.6</v>
       </c>
       <c r="AL7" s="1"/>
       <c r="AM7" s="4">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AN7" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="AO7" s="11">
-        <v>2.7</v>
+        <v>3.5</v>
+      </c>
+      <c r="AO7" s="4">
+        <v>3.7</v>
       </c>
       <c r="AP7" s="5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="4">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" s="4">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AU7" s="5">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AV7" s="1"/>
       <c r="AW7" s="4">
         <v>4.5</v>
       </c>
       <c r="AX7" s="4">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AY7" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7" s="5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BA7" s="1"/>
       <c r="BB7" s="1">
-        <v>3</v>
-      </c>
-      <c r="BC7" s="6">
-        <v>3.767</v>
+        <v>0</v>
+      </c>
+      <c r="BC7" s="7">
+        <v>4.056</v>
       </c>
       <c r="BD7" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:57">
@@ -3685,147 +4091,147 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="4">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="E8" s="4">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="F8" s="4">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="G8" s="5">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="4">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J8" s="4">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="K8" s="4">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L8" s="5">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="4">
+        <v>4</v>
+      </c>
+      <c r="O8" s="4">
         <v>4.3</v>
       </c>
-      <c r="O8" s="4">
-        <v>3.8</v>
-      </c>
       <c r="P8" s="4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" s="5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="4">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="T8" s="4">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U8" s="4">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="V8" s="5">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Y8" s="4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Z8" s="4">
         <v>4.3</v>
       </c>
       <c r="AA8" s="5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" s="4">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AE8" s="4">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AF8" s="5">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="4">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AI8" s="4">
         <v>3.6</v>
       </c>
-      <c r="AJ8" s="11">
-        <v>2.4</v>
+      <c r="AJ8" s="4">
+        <v>4.3</v>
       </c>
       <c r="AK8" s="5">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AL8" s="1"/>
       <c r="AM8" s="4">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AN8" s="4">
-        <v>3</v>
-      </c>
-      <c r="AO8" s="11">
-        <v>2.9</v>
+        <v>3.6</v>
+      </c>
+      <c r="AO8" s="4">
+        <v>3.6</v>
       </c>
       <c r="AP8" s="5">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="4">
         <v>4</v>
       </c>
       <c r="AS8" s="4">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AU8" s="5">
         <v>4.3</v>
-      </c>
-      <c r="AU8" s="5">
-        <v>4.1</v>
       </c>
       <c r="AV8" s="1"/>
       <c r="AW8" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX8" s="4">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AY8" s="4">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AZ8" s="5">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BA8" s="1"/>
       <c r="BB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="7">
+        <v>4.144</v>
+      </c>
+      <c r="BD8" s="1">
         <v>2</v>
-      </c>
-      <c r="BC8" s="6">
-        <v>3.667</v>
-      </c>
-      <c r="BD8" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:57">
@@ -3833,79 +4239,79 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="E9" s="4">
         <v>4.7</v>
       </c>
       <c r="F9" s="4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G9" s="5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="4">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J9" s="4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="L9" s="5">
         <v>4.4</v>
-      </c>
-      <c r="L9" s="5">
-        <v>4.6</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O9" s="4">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P9" s="4">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" s="5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T9" s="4">
         <v>4.4</v>
       </c>
       <c r="U9" s="4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="V9" s="5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="W9" s="1"/>
       <c r="X9" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AA9" s="5">
         <v>4.4</v>
-      </c>
-      <c r="Y9" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="Z9" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="AA9" s="5">
-        <v>4.3</v>
       </c>
       <c r="AB9" s="1"/>
       <c r="AC9" s="4">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" s="4">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AE9" s="4">
         <v>4.4</v>
@@ -3915,23 +4321,23 @@
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="AI9" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AJ9" s="4">
         <v>4.8</v>
       </c>
-      <c r="AI9" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="AJ9" s="4">
-        <v>4.5</v>
-      </c>
       <c r="AK9" s="5">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AL9" s="1"/>
       <c r="AM9" s="4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AN9" s="4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO9" s="4">
         <v>4.4</v>
@@ -3941,36 +4347,36 @@
       </c>
       <c r="AQ9" s="1"/>
       <c r="AR9" s="4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS9" s="4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" s="4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU9" s="5">
         <v>4.6</v>
       </c>
       <c r="AV9" s="1"/>
       <c r="AW9" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX9" s="4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AZ9" s="5">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" s="1"/>
       <c r="BB9" s="1">
         <v>0</v>
       </c>
-      <c r="BC9" s="6">
-        <v>4.5</v>
+      <c r="BC9" s="7">
+        <v>4.489</v>
       </c>
       <c r="BD9" s="1">
         <v>1</v>
@@ -3981,147 +4387,591 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="4">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4">
         <v>3.8</v>
       </c>
       <c r="F10" s="4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G10" s="5">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="4">
+        <v>4</v>
+      </c>
+      <c r="J10" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="K10" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="L10" s="5">
         <v>4.4</v>
-      </c>
-      <c r="J10" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K10" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="L10" s="5">
-        <v>4.3</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="4">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="O10" s="4">
         <v>4.1</v>
       </c>
       <c r="P10" s="4">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" s="5">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T10" s="4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U10" s="4">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="V10" s="5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="W10" s="1"/>
       <c r="X10" s="4">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" s="4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z10" s="4">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" s="5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD10" s="4">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AE10" s="4">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AF10" s="5">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AG10" s="1"/>
       <c r="AH10" s="4">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI10" s="4">
         <v>3.4</v>
       </c>
       <c r="AJ10" s="4">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AK10" s="5">
         <v>3.6</v>
       </c>
       <c r="AL10" s="1"/>
       <c r="AM10" s="4">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AN10" s="4">
         <v>3.7</v>
       </c>
       <c r="AO10" s="4">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AP10" s="5">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ10" s="1"/>
       <c r="AR10" s="4">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AS10" s="4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" s="4">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AU10" s="5">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AV10" s="1"/>
       <c r="AW10" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AX10" s="4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AY10" s="4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AZ10" s="5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BA10" s="1"/>
       <c r="BB10" s="1">
         <v>0</v>
       </c>
-      <c r="BC10" s="6">
-        <v>4.011</v>
+      <c r="BC10" s="7">
+        <v>4.033</v>
       </c>
       <c r="BD10" s="1">
-        <v>2</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="J11" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="K11" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="O11" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="P11" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="4">
+        <v>4</v>
+      </c>
+      <c r="T11" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="V11" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="W11" s="1"/>
+      <c r="X11" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="4">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AI11" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AJ11" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="AK11" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="AL11" s="1"/>
+      <c r="AM11" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="AN11" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="AO11" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AP11" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="AQ11" s="1"/>
+      <c r="AR11" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="AS11" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AT11" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="AU11" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="AV11" s="1"/>
+      <c r="AW11" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AX11" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AY11" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AZ11" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="BA11" s="1"/>
+      <c r="BB11" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="7">
+        <v>4.089</v>
+      </c>
+      <c r="BD11" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="E12" s="4">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="J12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="K12" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="O12" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="P12" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="T12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="U12" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="V12" s="5">
+        <v>4</v>
+      </c>
+      <c r="W12" s="1"/>
+      <c r="X12" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>4</v>
+      </c>
+      <c r="AE12" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="4">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="AJ12" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AK12" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN12" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AO12" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AP12" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="AQ12" s="1"/>
+      <c r="AR12" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="AS12" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AT12" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="AU12" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="AV12" s="1"/>
+      <c r="AW12" s="4">
+        <v>4</v>
+      </c>
+      <c r="AX12" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AY12" s="4">
+        <v>4</v>
+      </c>
+      <c r="AZ12" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="BA12" s="1"/>
+      <c r="BB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="7">
+        <v>4.033</v>
+      </c>
+      <c r="BD12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="4">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="J13" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="K13" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="L13" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="O13" s="4">
+        <v>4</v>
+      </c>
+      <c r="P13" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="T13" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="U13" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="V13" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="W13" s="1"/>
+      <c r="X13" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>4</v>
+      </c>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="AD13" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AE13" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AI13" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="AJ13" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AK13" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="AN13" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="AO13" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AP13" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="AQ13" s="1"/>
+      <c r="AR13" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="AS13" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AT13" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="AU13" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="AV13" s="1"/>
+      <c r="AW13" s="4">
+        <v>4</v>
+      </c>
+      <c r="AX13" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="AY13" s="4">
+        <v>4</v>
+      </c>
+      <c r="AZ13" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="BA13" s="1"/>
+      <c r="BB13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="7">
+        <v>4.1</v>
+      </c>
+      <c r="BD13" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4157,7 +5007,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BE8"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="2.285156" bestFit="true" customWidth="true" style="0"/>
@@ -4215,24 +5065,24 @@
     <col min="54" max="54" width="3" customWidth="true" style="0"/>
     <col min="55" max="55" width="7" customWidth="true" style="0"/>
     <col min="56" max="56" width="3" customWidth="true" style="0"/>
-    <col min="2" max="2" width="38.847656" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="42.418213" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:57" customHeight="1" ht="100">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -4246,7 +5096,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -4294,328 +5144,328 @@
       <c r="AY5" s="3"/>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="3"/>
-      <c r="BB5" s="7"/>
-      <c r="BC5" s="7"/>
-      <c r="BD5" s="7"/>
-      <c r="BE5" s="7"/>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
+      <c r="BD5" s="8"/>
+      <c r="BE5" s="8"/>
     </row>
     <row r="6" spans="1:57">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="10" t="s">
+      <c r="V6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="W6" s="10" t="s">
+      <c r="W6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="X6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Y6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Z6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AA6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="9" t="s">
+      <c r="AC6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="10" t="s">
+      <c r="AD6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AE6" s="10" t="s">
+      <c r="AE6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AF6" s="10" t="s">
+      <c r="AF6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AG6" s="10" t="s">
+      <c r="AG6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AH6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AI6" s="10" t="s">
+      <c r="AI6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AJ6" s="10" t="s">
+      <c r="AJ6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AK6" s="10" t="s">
+      <c r="AK6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AL6" s="10" t="s">
+      <c r="AL6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="9" t="s">
+      <c r="AM6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AN6" s="10" t="s">
+      <c r="AN6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AO6" s="10" t="s">
+      <c r="AO6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AP6" s="10" t="s">
+      <c r="AP6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AQ6" s="10" t="s">
+      <c r="AQ6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AR6" s="9" t="s">
+      <c r="AR6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AS6" s="10" t="s">
+      <c r="AS6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AT6" s="10" t="s">
+      <c r="AT6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AU6" s="10" t="s">
+      <c r="AU6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AV6" s="10" t="s">
+      <c r="AV6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AW6" s="9" t="s">
+      <c r="AW6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="AX6" s="10" t="s">
+      <c r="AX6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AY6" s="10" t="s">
+      <c r="AY6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AZ6" s="10" t="s">
+      <c r="AZ6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="BA6" s="10" t="s">
+      <c r="BA6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="BB6" s="10" t="s">
+      <c r="BB6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="BC6" s="10" t="s">
+      <c r="BC6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="BD6" s="10" t="s">
+      <c r="BD6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="BE6" s="7"/>
+      <c r="BE6" s="8"/>
     </row>
     <row r="7" spans="1:57">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="E7" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="G7" s="5">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J7" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K7" s="4">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L7" s="5">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="4">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O7" s="4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P7" s="4">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" s="5">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U7" s="4">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="V7" s="5">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="W7" s="1"/>
       <c r="X7" s="4">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y7" s="4">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Z7" s="4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA7" s="5">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="4">
         <v>3.9</v>
       </c>
       <c r="AD7" s="4">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AE7" s="4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF7" s="5">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="4">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AI7" s="4">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AJ7" s="4">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AK7" s="5">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AL7" s="1"/>
       <c r="AM7" s="4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AN7" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="AO7" s="4">
         <v>3.6</v>
       </c>
-      <c r="AO7" s="4">
-        <v>3.4</v>
-      </c>
       <c r="AP7" s="5">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AS7" s="4">
         <v>4.3</v>
       </c>
-      <c r="AS7" s="4">
-        <v>4.5</v>
-      </c>
       <c r="AT7" s="4">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AU7" s="5">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AV7" s="1"/>
       <c r="AW7" s="4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AX7" s="4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AY7" s="4">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7" s="5">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="BA7" s="1"/>
       <c r="BB7" s="1">
         <v>0</v>
       </c>
-      <c r="BC7" s="6">
-        <v>4.089</v>
+      <c r="BC7" s="7">
+        <v>3.744</v>
       </c>
       <c r="BD7" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:57">
@@ -4623,151 +5473,443 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="4">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="E8" s="4">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="F8" s="4">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="G8" s="5">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="4">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J8" s="4">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="K8" s="4">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="L8" s="5">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O8" s="4">
         <v>4.3</v>
       </c>
       <c r="P8" s="4">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" s="5">
         <v>4.3</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="4">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="T8" s="4">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U8" s="4">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="V8" s="5">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="4">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" s="4">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z8" s="4">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" s="5">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="4">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AD8" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="AE8" s="11">
-        <v>2.8</v>
+        <v>4.5</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>4.5</v>
       </c>
       <c r="AF8" s="5">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="4">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AI8" s="4">
-        <v>3</v>
-      </c>
-      <c r="AJ8" s="11">
-        <v>2.6</v>
-      </c>
-      <c r="AK8" s="12">
-        <v>2.9</v>
-      </c>
-      <c r="AL8" s="5">
-        <v>3</v>
-      </c>
-      <c r="AM8" s="11">
-        <v>2.8</v>
+        <v>4.3</v>
+      </c>
+      <c r="AJ8" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AK8" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="4">
+        <v>4.7</v>
       </c>
       <c r="AN8" s="4">
-        <v>3</v>
-      </c>
-      <c r="AO8" s="11">
-        <v>2.7</v>
-      </c>
-      <c r="AP8" s="12">
-        <v>2.8</v>
-      </c>
-      <c r="AQ8" s="5">
-        <v>3</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="AO8" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AP8" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="AQ8" s="1"/>
       <c r="AR8" s="4">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" s="4">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" s="4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" s="5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AV8" s="1"/>
       <c r="AW8" s="4">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" s="4">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AY8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ8" s="5">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="BA8" s="1"/>
       <c r="BB8" s="1">
-        <v>3</v>
-      </c>
-      <c r="BC8" s="6">
-        <v>3.444</v>
+        <v>0</v>
+      </c>
+      <c r="BC8" s="7">
+        <v>4.5</v>
       </c>
       <c r="BD8" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="F9" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="J9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="K9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4.6</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="O9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="P9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="T9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="U9" s="4">
+        <v>4</v>
+      </c>
+      <c r="V9" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="W9" s="1"/>
+      <c r="X9" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>4.9</v>
+      </c>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>4.6</v>
+      </c>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AI9" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AJ9" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AK9" s="5">
+        <v>4.4</v>
+      </c>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AN9" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="AO9" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AP9" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="AQ9" s="1"/>
+      <c r="AR9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AS9" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="AT9" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="AU9" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="AV9" s="1"/>
+      <c r="AW9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AX9" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AY9" s="4">
+        <v>4</v>
+      </c>
+      <c r="AZ9" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="BA9" s="1"/>
+      <c r="BB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="7">
+        <v>4.544</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="4">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="G10" s="5">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="J10" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="K10" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="L10" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="O10" s="4">
+        <v>4.1</v>
+      </c>
+      <c r="P10" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="T10" s="4">
+        <v>4</v>
+      </c>
+      <c r="U10" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="V10" s="5">
+        <v>4</v>
+      </c>
+      <c r="W10" s="1"/>
+      <c r="X10" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="AE10" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AJ10" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="AK10" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AN10" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="AO10" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="AP10" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="AQ10" s="1"/>
+      <c r="AR10" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="AS10" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AT10" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="AU10" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="AV10" s="1"/>
+      <c r="AW10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AX10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AY10" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AZ10" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="BA10" s="1"/>
+      <c r="BB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="7">
+        <v>3.878</v>
+      </c>
+      <c r="BD10" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
